--- a/out/LSTM-Mamba1_repeat_4_000001.xlsx
+++ b/out/LSTM-Mamba1_repeat_4_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
-        <v>-7.549743061384651e-05</v>
+        <v>-6.522884500527289e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.03250700163653785</v>
+        <v>0.02808564681070064</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.06510075586587261</v>
+        <v>0.05624624678713619</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1255909113784595</v>
+        <v>0.1085088794383322</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.2838603620831945</v>
+        <v>0.2452518374137715</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.03863297737825833</v>
+        <v>0.03337793958473097</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2353747611161221</v>
+        <v>0.2033608363725715</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.00783871192263551</v>
+        <v>0.006772323509422399</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2123591837899089</v>
+        <v>0.1834748228730182</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.006787130236714228</v>
+        <v>0.005863566622783443</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2180879121040965</v>
+        <v>0.1884236426376505</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.003315884100197597</v>
+        <v>0.002863672648104922</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.217924827968996</v>
+        <v>0.1882820691942722</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.001579903061546279</v>
+        <v>0.001364083631158653</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2177652469128931</v>
+        <v>0.188143505866406</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0006552583008062353</v>
+        <v>0.0005656279581166873</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.2174940408466905</v>
+        <v>0.187908437385919</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0004526011935854903</v>
+        <v>0.0003900958028933744</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.217743387102616</v>
+        <v>0.1881232567927102</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0001857089590046543</v>
+        <v>0.0001599374780580794</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.2176623513565788</v>
+        <v>0.1880524789126902</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>9.388939844386562e-05</v>
+        <v>8.052596622172162e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2176642463538488</v>
+        <v>0.1880534453850971</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>3.383994239731721e-05</v>
+        <v>2.859130153281488e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.2176377769955543</v>
+        <v>0.1880298579022884</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>1.618743066942789e-05</v>
+        <v>1.332426436274844e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.2176363164230874</v>
+        <v>0.1880279254918529</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>5.728762911577315e-06</v>
+        <v>4.034747715012475e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.2176309892779815</v>
+        <v>0.1880226420301429</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-2.045694596194254e-07</v>
+        <v>-7.373950752172664e-07</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.2176253723353827</v>
+        <v>0.1880170900940134</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-2.694140733653212e-06</v>
+        <v>-3.155312586922569e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.2176196491787541</v>
+        <v>0.1880114398288601</v>
       </c>
     </row>
     <row r="60">
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.2176144078574532</v>
+        <v>0.1880061985075593</v>
       </c>
     </row>
     <row r="61">
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2176091199186027</v>
+        <v>0.1880009105687088</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2176038480845517</v>
+        <v>0.1879956387346578</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.217603887940024</v>
+        <v>0.1879956785901301</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2176039277954963</v>
+        <v>0.1879957184456023</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2176039198244019</v>
+        <v>0.1879957104745079</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.217604079246291</v>
+        <v>0.187995869896397</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2176039835931575</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2176043343213138</v>
+        <v>0.1879961249714198</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2176040872173854</v>
+        <v>0.1879958778674914</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2176040473619131</v>
+        <v>0.1879958380120192</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2176039835931575</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2176040553330076</v>
+        <v>0.1879958459831136</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2176039835931575</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2176040872173854</v>
+        <v>0.1879958778674914</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2176041828705191</v>
+        <v>0.1879959735206251</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2176041191017632</v>
+        <v>0.1879959097518693</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.217604079246291</v>
+        <v>0.187995869896397</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2176040553330076</v>
+        <v>0.1879958459831136</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2176038082290795</v>
+        <v>0.1879955988791855</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2176037285181347</v>
+        <v>0.1879955191682407</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2176037763447014</v>
+        <v>0.1879955669948075</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2176038959111185</v>
+        <v>0.1879956865612245</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2176038799689296</v>
+        <v>0.1879956706190356</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2176038959111185</v>
+        <v>0.1879956865612245</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2176038799689296</v>
+        <v>0.1879956706190356</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2176039357665908</v>
+        <v>0.1879957264166968</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2176039357665908</v>
+        <v>0.1879957264166968</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2176039357665908</v>
+        <v>0.1879957264166968</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2176040872173854</v>
+        <v>0.1879958778674914</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.217604302436936</v>
+        <v>0.187996093087042</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2176042147548969</v>
+        <v>0.187996005405003</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2176041669283302</v>
+        <v>0.1879959575784362</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2176042147548969</v>
+        <v>0.187996005405003</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2176040314197242</v>
+        <v>0.1879958220698303</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2176040393908187</v>
+        <v>0.1879958300409247</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2176040473619131</v>
+        <v>0.1879958380120192</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2176040553330076</v>
+        <v>0.1879958459831136</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2176040553330076</v>
+        <v>0.1879958459831136</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2176040951884799</v>
+        <v>0.1879958858385859</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2176041589572358</v>
+        <v>0.1879959496073418</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2176042705525581</v>
+        <v>0.1879960612026642</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2176043183791249</v>
+        <v>0.1879961090292309</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2176042785236526</v>
+        <v>0.1879960691737586</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2176042067838025</v>
+        <v>0.1879959974339085</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2176043263502193</v>
+        <v>0.1879961170003253</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2176041669283302</v>
+        <v>0.1879959575784362</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2176039357665908</v>
+        <v>0.1879957264166968</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.217603887940024</v>
+        <v>0.1879956785901301</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2176039198244019</v>
+        <v>0.1879957104745079</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2176039835931575</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2176039835931575</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2176039038822129</v>
+        <v>0.187995694532319</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2176037843157959</v>
+        <v>0.1879955749659019</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2176037444603236</v>
+        <v>0.1879955351104296</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.217603887940024</v>
+        <v>0.1879956785901301</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2176040234486298</v>
+        <v>0.1879958140987358</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2176040075064408</v>
+        <v>0.1879957981565469</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2176039835931575</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2176039437376852</v>
+        <v>0.1879957343877912</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2176038401134573</v>
+        <v>0.1879956307635633</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2176037205470402</v>
+        <v>0.1879955111971462</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2176038401134573</v>
+        <v>0.1879956307635633</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.217603887940024</v>
+        <v>0.1879956785901301</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2176039835931575</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2176038640267406</v>
+        <v>0.1879956546768467</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2176038719978351</v>
+        <v>0.1879956626479412</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_4_000001.xlsx
+++ b/out/LSTM-Mamba1_repeat_4_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,17 +35122,17 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC43" t="n">
-        <v>-7.549743061384651e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.03250700163653785</v>
+        <v>0</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.06510075586587261</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1255909113784595</v>
+        <v>0</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.2838603620831945</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.03863297737825833</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2353747611161221</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.00783871192263551</v>
+        <v>0</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2123591837899089</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39093,21 +39093,21 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.006787130236714228</v>
+        <v>0</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2180879121040965</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.003315884100197597</v>
+        <v>0</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.217924827968996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.001579903061546279</v>
+        <v>0</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2177652469128931</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0006552583008062353</v>
+        <v>0</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.2174940408466905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0004526011935854903</v>
+        <v>0</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.217743387102616</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0001857089590046543</v>
+        <v>0</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.2176623513565788</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>9.388939844386562e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2176642463538488</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>3.383994239731721e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.2176377769955543</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>1.618743066942789e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.2176363164230874</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>5.728762911577315e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.2176309892779815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-2.045694596194254e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.2176253723353827</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-2.694140733653212e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.2176196491787541</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-4.173194643232597e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.2176144078574532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.68213567138761e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2176091199186027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.817481666896968e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2176038480845517</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -51022,17 +51022,17 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.217603887940024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -51817,17 +51817,17 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2176039277954963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -52612,17 +52612,17 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2176039198244019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -53407,17 +53407,17 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.217604079246291</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -54202,17 +54202,17 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2176039835931575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2176043343213138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2176040872173854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2176040473619131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2176039835931575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2176040553330076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2176039835931575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2176040872173854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2176041828705191</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2176041191017632</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.217604079246291</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2176040553330076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2176038082290795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2176037285181347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2176037763447014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2176038959111185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2176038799689296</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2176038959111185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2176038799689296</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2176039357665908</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2176039357665908</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2176039357665908</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2176040872173854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.217604302436936</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2176042147548969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2176041669283302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2176042147548969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2176040314197242</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2176040393908187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2176040473619131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2176040553330076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2176040553330076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2176040951884799</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2176041589572358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2176042705525581</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2176043183791249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2176042785236526</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2176042067838025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2176043263502193</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2176041669283302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2176039357665908</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.217603887940024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2176039198244019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2176039835931575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2176039835931575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2176039038822129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2176037843157959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2176037444603236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.217603887940024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2176040234486298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2176040075064408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2176039835931575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2176039437376852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2176038401134573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2176037205470402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2176038401134573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.217603887940024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2176039835931575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2176038640267406</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-4.79359707945414e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell (Force)</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2176038719978351</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_4_000001.xlsx
+++ b/out/LSTM-Mamba1_repeat_4_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.002124400576576591</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.001541811507195234</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3699999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.00121722009498626</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.001029878854751587</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.0009056620765477419</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.0008096722885966301</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.0007355471607297659</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.0006802568677812815</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.0006474251858890057</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.0006374020595103502</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.0006287952419370413</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.0006163362413644791</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.0006032213568687439</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.0006122945342212915</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.0006404807791113853</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.0006924082990735769</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.0007429553661495447</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.0007869179826229811</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.0008253618143498898</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.0008676364086568356</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.0008973740041255951</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.000904289074242115</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.0008848684374243021</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.0008434276096522808</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.0008065067231655121</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.0007707490585744381</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.0007383008487522602</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.0007098324131220579</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.000694292364642024</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.0006701080128550529</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.0006344127468764782</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.000592866213992238</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.0005403703544288874</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.0005041975528001785</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.0004774404224008322</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.0004653502255678177</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.0004681306891143322</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.0004906791727989912</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.0005428793374449015</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.0006441820878535509</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.0007637885864824057</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,17 +35122,17 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.000956549309194088</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>0</v>
+        <v>-2.975905342493206e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0</v>
+        <v>0.01281327730767792</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.001188084599561989</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>0.02566096483563806</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.04950529396035906</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.001543342135846615</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>0.1118908286762438</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>0.01522759692281715</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.001828876207582653</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>0.09277907819874584</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0</v>
+        <v>0.003086838631631702</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.00196061423048377</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>0.08370368467059662</v>
       </c>
     </row>
     <row r="48">
@@ -39093,21 +39093,21 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0</v>
+        <v>0.002672618539613283</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.002055977704003453</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>0.08595893670423399</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.001304033150794584</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.002108907327055931</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>0.08589162276396481</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.0006197404563852321</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.002151905093342066</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>0.08582568967481796</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.0002549836648199931</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.002168437698855996</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0</v>
+        <v>0.08571575663521513</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.0001755711286661125</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.002193927299231291</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0</v>
+        <v>0.0858111226114151</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>7.038158176873161e-05</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.002195454435423017</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0</v>
+        <v>0.08577611835331517</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>3.375395344421761e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.002186967758461833</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0</v>
+        <v>0.08577383498870163</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0</v>
+        <v>1.022105850705674e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.002166258171200752</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0</v>
+        <v>0.08576033407009277</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0</v>
+        <v>3.589498920038333e-06</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.002145465463399887</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0</v>
+        <v>0.085756749583998</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0</v>
+        <v>-1.047297874682042e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.00212710932828486</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0</v>
+        <v>0.08575162108575948</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0</v>
+        <v>-2.868697537608634e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.002100640442222357</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0</v>
+        <v>0.08574636105988361</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0</v>
+        <v>-4.077656293461284e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.002064082305878401</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0</v>
+        <v>0.08574107179723191</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>-4.586597321616299e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.002026220317929983</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0</v>
+        <v>0.08573597504986473</v>
       </c>
     </row>
     <row r="61">
@@ -49432,17 +49432,17 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.001972890691831708</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0</v>
+        <v>0.08573587939673126</v>
       </c>
     </row>
     <row r="62">
@@ -50227,17 +50227,17 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.001907967147417367</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0</v>
+        <v>0.08573574388812552</v>
       </c>
     </row>
     <row r="63">
@@ -51022,17 +51022,17 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.001863516285084188</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0</v>
+        <v>0.0857357837435978</v>
       </c>
     </row>
     <row r="64">
@@ -51817,17 +51817,17 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.001836922136135399</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0</v>
+        <v>0.08573582359907007</v>
       </c>
     </row>
     <row r="65">
@@ -52612,17 +52612,17 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.001831236644648015</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0</v>
+        <v>0.08573581562797562</v>
       </c>
     </row>
     <row r="66">
@@ -53407,17 +53407,17 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.001851391396485269</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0</v>
+        <v>0.08573597504986473</v>
       </c>
     </row>
     <row r="67">
@@ -54202,17 +54202,17 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.001875669695436954</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0</v>
+        <v>0.08573587939673126</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.001937963999807835</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0</v>
+        <v>0.08573623012488754</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.001962671522051096</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0</v>
+        <v>0.08573598302095919</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.001965084578841925</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0</v>
+        <v>0.08573594316548691</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.001953047350980341</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC71" t="n">
-        <v>0</v>
+        <v>0.08573587939673126</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.001944199437275529</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC72" t="n">
-        <v>0</v>
+        <v>0.08573595113658136</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.001924175070598722</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0</v>
+        <v>0.08573587939673126</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.001917493063956499</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0</v>
+        <v>0.08573598302095919</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.00194482842925936</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0</v>
+        <v>0.08573607867409289</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.001968026626855135</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0</v>
+        <v>0.08573601490533701</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.001972474157810211</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0</v>
+        <v>0.08573597504986473</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.001949708093889058</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0</v>
+        <v>0.08573595113658136</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.001887678634375334</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0</v>
+        <v>0.08573570403265325</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.001819040859118104</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0</v>
+        <v>0.08573562432170846</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.001772165996953845</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0</v>
+        <v>0.08573567214827518</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.001756976009346545</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0</v>
+        <v>0.08573579171469226</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.001752061652950943</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0</v>
+        <v>0.08573577577250334</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.001752684125676751</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0</v>
+        <v>0.08573579171469226</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.001759195816703141</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0</v>
+        <v>0.08573577577250334</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.001774689182639122</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC86" t="n">
-        <v>0</v>
+        <v>0.08573583157016454</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.001788141671568155</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC87" t="n">
-        <v>0</v>
+        <v>0.08573583157016454</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.001803672523237765</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>0</v>
+        <v>0.08573583157016454</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.00184262462425977</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0</v>
+        <v>0.08573598302095919</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.001899150898680091</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0</v>
+        <v>0.08573619824050972</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.001950530218891799</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0</v>
+        <v>0.0857361105584707</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.00198422628454864</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0</v>
+        <v>0.08573606273190398</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.002002556342631578</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0</v>
+        <v>0.0857361105584707</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.001986815361306071</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0</v>
+        <v>0.08573592722329799</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.001963117159903049</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0</v>
+        <v>0.08573593519439246</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.001945131924003363</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0</v>
+        <v>0.08573594316548691</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.001935248379595578</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0</v>
+        <v>0.08573595113658136</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.00192881585098803</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0</v>
+        <v>0.08573595113658136</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.001934033469296992</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0</v>
+        <v>0.08573599099205365</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.001957607688382268</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0</v>
+        <v>0.08573605476080952</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.002000553999096155</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0</v>
+        <v>0.0857361663561319</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.002040979918092489</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0</v>
+        <v>0.08573621418269864</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.002061829203739762</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0</v>
+        <v>0.08573617432722636</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.002074526622891426</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0</v>
+        <v>0.08573610258737625</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.002088143955916166</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0</v>
+        <v>0.08573622215379309</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.00206246692687273</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0</v>
+        <v>0.08573606273190398</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.002002697438001633</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0</v>
+        <v>0.08573583157016454</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.00193583860527724</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC108" t="n">
-        <v>0</v>
+        <v>0.0857357837435978</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.001891061663627625</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0</v>
+        <v>0.08573581562797562</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.001869723200798035</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0</v>
+        <v>0.08573587939673126</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.001853920752182603</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0</v>
+        <v>0.08573587939673126</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.001829287852160633</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0</v>
+        <v>0.08573579968578671</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.001785562839359045</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0</v>
+        <v>0.08573568011936965</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.00174816488288343</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0</v>
+        <v>0.08573564026389736</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.001745781046338379</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0</v>
+        <v>0.0857357837435978</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.001770462957210839</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0</v>
+        <v>0.08573591925220354</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.001796798082068563</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0</v>
+        <v>0.08573590331001463</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.001808640314266086</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC118" t="n">
-        <v>0</v>
+        <v>0.08573587939673126</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.00180557300336659</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC119" t="n">
-        <v>0</v>
+        <v>0.08573583954125899</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.001776635646820068</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC120" t="n">
-        <v>0</v>
+        <v>0.08573573591703107</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.00173798599280417</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0</v>
+        <v>0.085735616350614</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.001725390669889748</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0</v>
+        <v>0.08573573591703107</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.001734539051540196</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0</v>
+        <v>0.0857357837435978</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.001755461562424898</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0</v>
+        <v>0.08573587939673126</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.001761236344464123</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999995</v>
       </c>
       <c r="JC125" t="n">
-        <v>0</v>
+        <v>0.08573575983031444</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-4.79359707945414e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.001761394902132452</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000046</v>
       </c>
       <c r="JC126" t="n">
-        <v>0</v>
+        <v>0.08573576780140889</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_4_000001.xlsx
+++ b/out/LSTM-Mamba1_repeat_4_000001.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.002124400576576591</v>
+        <v>-0.00212439987808466</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.7199999999999999</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.00121722009498626</v>
+        <v>-0.001217219862155616</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.02000000000000007</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.001029878854751587</v>
+        <v>-0.00102988095022738</v>
       </c>
       <c r="JB5" t="n">
         <v>0.8599999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.0009056620765477419</v>
+        <v>-0.0009056637063622475</v>
       </c>
       <c r="JB6" t="n">
         <v>0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.0008096722885966301</v>
+        <v>-0.0008096729870885611</v>
       </c>
       <c r="JB7" t="n">
         <v>0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.0007355471607297659</v>
+        <v>-0.0007355480920523405</v>
       </c>
       <c r="JB8" t="n">
         <v>0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.0006802568677812815</v>
+        <v>-0.000680253142490983</v>
       </c>
       <c r="JB9" t="n">
         <v>0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.0006474251858890057</v>
+        <v>-0.0006474235560745001</v>
       </c>
       <c r="JB10" t="n">
         <v>0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.0006374020595103502</v>
+        <v>-0.0006374018266797066</v>
       </c>
       <c r="JB11" t="n">
         <v>0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.0006287952419370413</v>
+        <v>-0.0006287964060902596</v>
       </c>
       <c r="JB12" t="n">
         <v>0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.0006163362413644791</v>
+        <v>-0.0006163367070257664</v>
       </c>
       <c r="JB13" t="n">
         <v>0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.0006032213568687439</v>
+        <v>-0.0006032211240381002</v>
       </c>
       <c r="JB14" t="n">
         <v>0.2599999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.0006122945342212915</v>
+        <v>-0.0006122952327132225</v>
       </c>
       <c r="JB15" t="n">
         <v>0.1199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.0006404807791113853</v>
+        <v>-0.00064048171043396</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.02000000000000007</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.0007429553661495447</v>
+        <v>-0.0007429555989801884</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.3</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.0007869179826229811</v>
+        <v>-0.0007869189139455557</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.3</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.0008253618143498898</v>
+        <v>-0.0008253608830273151</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.3</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.0008676364086568356</v>
+        <v>-0.0008676387369632721</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.4399999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.0008973740041255951</v>
+        <v>-0.0008973747026175261</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.4399999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.000904289074242115</v>
+        <v>-0.0009042911697179079</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.4399999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.0008848684374243021</v>
+        <v>-0.0008848703000694513</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.3</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.0008434276096522808</v>
+        <v>-0.0008434290066361427</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.16</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.0008065067231655121</v>
+        <v>-0.0008065083529800177</v>
       </c>
       <c r="JB26" t="n">
         <v>0.7199999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.0007707490585744381</v>
+        <v>-0.0007707523182034492</v>
       </c>
       <c r="JB27" t="n">
         <v>0.8599999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.0007383008487522602</v>
+        <v>-0.0007382985204458237</v>
       </c>
       <c r="JB28" t="n">
         <v>0.9999999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.0007098324131220579</v>
+        <v>-0.0007098312489688396</v>
       </c>
       <c r="JB29" t="n">
         <v>0.9999999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.000694292364642024</v>
+        <v>-0.0006942914333194494</v>
       </c>
       <c r="JB30" t="n">
         <v>0.9999999999999998</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.0006701080128550529</v>
+        <v>-0.0006701082456856966</v>
       </c>
       <c r="JB31" t="n">
         <v>0.9999999999999998</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.0006344127468764782</v>
+        <v>-0.0006344120483845472</v>
       </c>
       <c r="JB32" t="n">
         <v>0.9999999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.000592866213992238</v>
+        <v>-0.0005928650498390198</v>
       </c>
       <c r="JB33" t="n">
         <v>0.9999999999999998</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.0005403703544288874</v>
+        <v>-0.000540371285751462</v>
       </c>
       <c r="JB34" t="n">
         <v>0.9999999999999998</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.0005041975528001785</v>
+        <v>-0.0005041994154453278</v>
       </c>
       <c r="JB35" t="n">
         <v>0.9999999999999998</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.0004774404224008322</v>
+        <v>-0.0004774415865540504</v>
       </c>
       <c r="JB36" t="n">
         <v>0.9999999999999998</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.0004653502255678177</v>
+        <v>-0.000465350691229105</v>
       </c>
       <c r="JB37" t="n">
         <v>0.3999999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.0004681306891143322</v>
+        <v>-0.0004681327845901251</v>
       </c>
       <c r="JB38" t="n">
         <v>0.2599999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.0004906791727989912</v>
+        <v>-0.0004906817339360714</v>
       </c>
       <c r="JB39" t="n">
         <v>0.1199999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.0005428793374449015</v>
+        <v>-0.0005428814329206944</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.16</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.0006441820878535509</v>
+        <v>-0.0006441830191761255</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.4399999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.0007637885864824057</v>
+        <v>-0.0007637839298695326</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.7199999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.000956549309194088</v>
+        <v>-0.0009565490763634443</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.8599999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.001188084599561989</v>
+        <v>-0.001188079360872507</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.001543342135846615</v>
+        <v>-0.001543341786600649</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.001828876207582653</v>
+        <v>-0.001828876556828618</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.00196061423048377</v>
+        <v>-0.001960615161806345</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.002055977704003453</v>
+        <v>-0.00205598771572113</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.002108907327055931</v>
+        <v>-0.002108914311975241</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.002151905093342066</v>
+        <v>-0.002151910215616226</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.002168437698855996</v>
+        <v>-0.002168442122638226</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.002193927299231291</v>
+        <v>-0.002193929394707084</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.002195454435423017</v>
+        <v>-0.002195447217673063</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.002186967758461833</v>
+        <v>-0.002186964266002178</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.002166258171200752</v>
+        <v>-0.002166255377233028</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.002145465463399887</v>
+        <v>-0.002145463135093451</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.00212710932828486</v>
+        <v>-0.002127107698470354</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.002100640442222357</v>
+        <v>-0.002100640209391713</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.002064082305878401</v>
+        <v>-0.002064086031168699</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.002026220317929983</v>
+        <v>-0.002026221016421914</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.001972890691831708</v>
+        <v>-0.00197288952767849</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.001907967147417367</v>
+        <v>-0.001907966565340757</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.001863516285084188</v>
+        <v>-0.001863515703007579</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.001836922136135399</v>
+        <v>-0.00183692411519587</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.001831236644648015</v>
+        <v>-0.001831240253522992</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.9999999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.001851391396485269</v>
+        <v>-0.00185139337554574</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.9999999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.001875669695436954</v>
+        <v>-0.00187567132525146</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.001937963999807835</v>
+        <v>-0.001937966677360237</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.9999999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.001962671522051096</v>
+        <v>-0.001962671289220452</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.001965084578841925</v>
+        <v>-0.00196508620865643</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.2599999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.001953047350980341</v>
+        <v>-0.001953047816641629</v>
       </c>
       <c r="JB71" t="n">
         <v>0.02000000000000007</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.001944199437275529</v>
+        <v>-0.001944200601428747</v>
       </c>
       <c r="JB72" t="n">
         <v>0.3</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.001924175070598722</v>
+        <v>-0.001924178446643054</v>
       </c>
       <c r="JB73" t="n">
         <v>0.5799999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.001917493063956499</v>
+        <v>-0.001917496556416154</v>
       </c>
       <c r="JB74" t="n">
         <v>0.7199999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.00194482842925936</v>
+        <v>-0.001944831921719015</v>
       </c>
       <c r="JB75" t="n">
         <v>0.7199999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.001968026626855135</v>
+        <v>-0.001968029420822859</v>
       </c>
       <c r="JB76" t="n">
         <v>0.5799999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.001972474157810211</v>
+        <v>-0.001972475089132786</v>
       </c>
       <c r="JB77" t="n">
         <v>0.5799999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.001949708093889058</v>
+        <v>-0.00194970949087292</v>
       </c>
       <c r="JB78" t="n">
         <v>0.5799999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.001887678634375334</v>
+        <v>-0.001887682010419667</v>
       </c>
       <c r="JB79" t="n">
         <v>0.7199999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.001819040859118104</v>
+        <v>-0.001819042023271322</v>
       </c>
       <c r="JB80" t="n">
         <v>0.8599999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.001756976009346545</v>
+        <v>-0.00175697763916105</v>
       </c>
       <c r="JB82" t="n">
         <v>0.9999999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.001752061652950943</v>
+        <v>-0.001752065145410597</v>
       </c>
       <c r="JB83" t="n">
         <v>0.9999999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.001752684125676751</v>
+        <v>-0.001752688200213015</v>
       </c>
       <c r="JB84" t="n">
         <v>0.8599999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.001759195816703141</v>
+        <v>-0.001759202335961163</v>
       </c>
       <c r="JB85" t="n">
         <v>0.7199999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.001774689182639122</v>
+        <v>-0.001774693839251995</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.02000000000000007</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.001788141671568155</v>
+        <v>-0.001788144232705235</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.16</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.001803672523237765</v>
+        <v>-0.001803675666451454</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.3</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.00184262462425977</v>
+        <v>-0.001842625206336379</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.4399999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.001899150898680091</v>
+        <v>-0.001899151713587344</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.5799999999999998</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.001950530218891799</v>
+        <v>-0.001950530684553087</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.7199999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.00198422628454864</v>
+        <v>-0.001984227681532502</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.8599999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.001986815361306071</v>
+        <v>-0.001986816059798002</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.9999999999999998</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.001963117159903049</v>
+        <v>-0.001963116228580475</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.9999999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.001945131924003363</v>
+        <v>-0.001945142168551683</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.9999999999999998</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.001935248379595578</v>
+        <v>-0.001935254433192313</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.9999999999999998</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.00192881585098803</v>
+        <v>-0.001928822253830731</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.9999999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.001934033469296992</v>
+        <v>-0.001934039988555014</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.9999999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.001957607688382268</v>
+        <v>-0.00195761164650321</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.9999999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.002000553999096155</v>
+        <v>-0.00200056005269289</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.9999999999999998</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.002040979918092489</v>
+        <v>-0.002040981547906995</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.9999999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.002061829203739762</v>
+        <v>-0.002061830833554268</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.9999999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.002074526622891426</v>
+        <v>-0.002074527088552713</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.9999999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.002088143955916166</v>
+        <v>-0.002088143024593592</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.00206246692687273</v>
+        <v>-0.002062467625364661</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.2599999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.00193583860527724</v>
+        <v>-0.001935837441124022</v>
       </c>
       <c r="JB108" t="n">
         <v>0.16</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.001891061663627625</v>
+        <v>-0.001891061547212303</v>
       </c>
       <c r="JB109" t="n">
         <v>0.4399999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.001869723200798035</v>
+        <v>-0.001869725296273828</v>
       </c>
       <c r="JB110" t="n">
         <v>0.7199999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.001853920752182603</v>
+        <v>-0.001853924128226936</v>
       </c>
       <c r="JB111" t="n">
         <v>0.8599999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.001829287852160633</v>
+        <v>-0.001829291461035609</v>
       </c>
       <c r="JB112" t="n">
         <v>0.9999999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.001785562839359045</v>
+        <v>-0.001785567263141274</v>
       </c>
       <c r="JB113" t="n">
         <v>0.9999999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.00174816488288343</v>
+        <v>-0.001748167560435832</v>
       </c>
       <c r="JB114" t="n">
         <v>0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.001745781046338379</v>
+        <v>-0.001745782676152885</v>
       </c>
       <c r="JB115" t="n">
         <v>0.9999999999999998</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.001770462957210839</v>
+        <v>-0.001770465867593884</v>
       </c>
       <c r="JB116" t="n">
         <v>0.8599999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.001796798082068563</v>
+        <v>-0.001796799129806459</v>
       </c>
       <c r="JB117" t="n">
         <v>0.7199999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.001808640314266086</v>
+        <v>-0.001808643108233809</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.02000000000000007</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.00180557300336659</v>
+        <v>-0.001805574516765773</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.02000000000000007</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.001776635646820068</v>
+        <v>-0.001776636694557965</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.02000000000000007</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.00173798599280417</v>
+        <v>-0.001737984246574342</v>
       </c>
       <c r="JB121" t="n">
         <v>0.1199999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.001725390669889748</v>
+        <v>-0.001725391019135714</v>
       </c>
       <c r="JB122" t="n">
         <v>0.2599999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.001734539051540196</v>
+        <v>-0.001734538818709552</v>
       </c>
       <c r="JB123" t="n">
         <v>0.9999999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.001755461562424898</v>
+        <v>-0.00175546295940876</v>
       </c>
       <c r="JB124" t="n">
         <v>0.8599999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.001761236344464123</v>
+        <v>-0.00176123552955687</v>
       </c>
       <c r="JB125" t="n">
         <v>0.7199999999999995</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.001761394902132452</v>
+        <v>-0.001761395018547773</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.02000000000000046</v>
